--- a/SHGraduationWarning/Template/學期成績與課規比對樣板.xlsx
+++ b/SHGraduationWarning/Template/學期成績與課規比對樣板.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ischoolProject\ScoreReportDAL\SHGraduationWarning\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F72678-EFA9-41DE-998D-FF80979832BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D5914E-4753-40C6-8F74-EB3EE9F6EA00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{858E2159-7E00-42C1-989A-9B7904A40F9C}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21585" windowHeight="11295" xr2:uid="{858E2159-7E00-42C1-989A-9B7904A40F9C}"/>
   </bookViews>
   <sheets>
-    <sheet name="依學期成績為主比對課規不符合" sheetId="1" r:id="rId1"/>
-    <sheet name="依課規為主比對學期成績不符合" sheetId="2" r:id="rId2"/>
-    <sheet name="依課規比對課程群組學分總數不符合" sheetId="3" r:id="rId3"/>
+    <sheet name="學期科目成績比對" sheetId="1" r:id="rId1"/>
+    <sheet name="課程規劃比對" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
   <si>
     <t>學號</t>
   </si>
@@ -71,12 +70,6 @@
   </si>
   <si>
     <t>使用課規</t>
-  </si>
-  <si>
-    <t>分組名稱</t>
-  </si>
-  <si>
-    <t>分組修課學分數</t>
   </si>
   <si>
     <t>學生系統編號</t>
@@ -105,9 +98,6 @@
   </si>
   <si>
     <t>領域</t>
-  </si>
-  <si>
-    <t>成績累計學分數</t>
   </si>
   <si>
     <t>分項類別</t>
@@ -187,9 +177,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -227,7 +217,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -333,7 +323,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -475,7 +465,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -491,7 +481,7 @@
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -524,19 +514,19 @@
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>10</v>
@@ -570,7 +560,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -579,7 +569,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -588,68 +578,12 @@
         <v>9</v>
       </c>
       <c r="L1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65180E6E-8E53-4620-842D-0DE38B85770E}">
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5" customWidth="1"/>
-    <col min="3" max="5" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="16.125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
